--- a/artfynd/A 38318-2019 artfynd.xlsx
+++ b/artfynd/A 38318-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38318-2019 artfynd.xlsx
+++ b/artfynd/A 38318-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12950,6 +12950,118 @@
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>125624439</v>
+      </c>
+      <c r="B109" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Möckeltjärnmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>539456</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6918945</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Lizette Karström</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Lizette Karström</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38318-2019 artfynd.xlsx
+++ b/artfynd/A 38318-2019 artfynd.xlsx
@@ -12955,12 +12955,7 @@
         <v>125624439</v>
       </c>
       <c r="B109" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2019 artfynd.xlsx
+++ b/artfynd/A 38318-2019 artfynd.xlsx
@@ -12955,7 +12955,7 @@
         <v>125624439</v>
       </c>
       <c r="B109" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2019 artfynd.xlsx
+++ b/artfynd/A 38318-2019 artfynd.xlsx
@@ -12955,7 +12955,7 @@
         <v>125624439</v>
       </c>
       <c r="B109" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2019 artfynd.xlsx
+++ b/artfynd/A 38318-2019 artfynd.xlsx
@@ -12955,7 +12955,7 @@
         <v>125624439</v>
       </c>
       <c r="B109" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2019 artfynd.xlsx
+++ b/artfynd/A 38318-2019 artfynd.xlsx
@@ -12955,7 +12955,7 @@
         <v>125624439</v>
       </c>
       <c r="B109" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
